--- a/assets/PMOS_Recovery_Command_Center.xlsx
+++ b/assets/PMOS_Recovery_Command_Center.xlsx
@@ -1882,475 +1882,475 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="35" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="35" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="42" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="42" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="176" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="176" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="47" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3893,9 +3893,9 @@
   <dimension ref="B2:F37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9415,7 +9415,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7FEC3E41-00BC-49DD-8E20-1013ABDCFB79}</x14:id>
+          <x14:id>{6D58193E-DA60-4FB6-9DEF-86C68AD966B0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9449,7 +9449,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7FEC3E41-00BC-49DD-8E20-1013ABDCFB79}">
+          <x14:cfRule type="dataBar" id="{6D58193E-DA60-4FB6-9DEF-86C68AD966B0}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
